--- a/outputs/41265.xlsx
+++ b/outputs/41265.xlsx
@@ -188,48 +188,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -425,105 +429,105 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="20.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D2&amp;" "," "&amp;A$2:A$6&amp;" ")),B$2:B$6)</f>
+      <c r="E2" s="8" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D2&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
         <v>80</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D3&amp;" "," "&amp;A$2:A$6&amp;" ")),B$2:B$6)</f>
+      <c r="E3" s="8" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D3&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
         <v>70</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D4&amp;" "," "&amp;A$2:A$6&amp;" ")),B$2:B$6)</f>
+      <c r="E4" s="8" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D4&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
         <v>80</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D5&amp;" "," "&amp;A$2:A$6&amp;" ")),B$2:B$6)</f>
+      <c r="E5" s="10" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D5&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
         <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I17" s="10"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I21" s="10"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="10"/>
+      <c r="I28" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/41265.xlsx
+++ b/outputs/41265.xlsx
@@ -463,8 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="8" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D2&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -478,8 +477,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="8" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D3&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -493,8 +491,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="8" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D4&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -508,8 +505,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="10" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(" "&amp;D5&amp;" "," "&amp;$A$2:$A$6&amp;" ")),$B$2:$B$6)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -517,6 +513,9 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>50</v>
       </c>
     </row>
